--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9764567</v>
+        <v>4808687</v>
       </c>
       <c r="L2" t="n">
-        <v>6001289</v>
+        <v>2877136</v>
       </c>
       <c r="M2" t="n">
-        <v>1532307</v>
+        <v>723594</v>
       </c>
       <c r="N2" t="n">
-        <v>58888</v>
+        <v>21572</v>
       </c>
       <c r="O2" t="n">
-        <v>885789</v>
+        <v>419161</v>
       </c>
       <c r="P2" t="n">
-        <v>302865</v>
+        <v>141873</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9536800384521484</v>
+        <v>0.9328058958053589</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9078950881958008</v>
+        <v>0.877704381942749</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8939571976661682</v>
+        <v>0.8380925059318542</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3780833780765533</v>
+        <v>0.2964734435081482</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8836091160774231</v>
+        <v>0.8419896960258484</v>
       </c>
       <c r="W2" t="n">
-        <v>0.973094642162323</v>
+        <v>0.9510890245437622</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>724</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>9764567</v>
+        <v>4808687</v>
       </c>
       <c r="E3" t="n">
-        <v>305263</v>
+        <v>223580</v>
       </c>
       <c r="F3" t="n">
-        <v>2120</v>
+        <v>1294</v>
       </c>
       <c r="G3" t="n">
-        <v>319</v>
+        <v>192</v>
       </c>
       <c r="H3" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>20032474</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>22111902</v>
+        <v>10949071</v>
       </c>
       <c r="L3" t="n">
-        <v>25535706</v>
+        <v>12669359</v>
       </c>
       <c r="M3" t="n">
-        <v>30614269</v>
+        <v>15258000</v>
       </c>
       <c r="N3" t="n">
-        <v>32384265</v>
+        <v>16189346</v>
       </c>
       <c r="O3" t="n">
-        <v>31524764</v>
+        <v>15741966</v>
       </c>
       <c r="P3" t="n">
-        <v>32264281</v>
+        <v>16129022</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9693767428398132</v>
+        <v>0.9552155733108521</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9211961627006531</v>
+        <v>0.8827322721481323</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8224210739135742</v>
+        <v>0.7765450477600098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3307032585144043</v>
+        <v>0.2422078549861908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8703336119651794</v>
+        <v>0.8235427141189575</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7835180759429932</v>
+        <v>0.7340207695960999</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>433766</v>
+        <v>318231</v>
       </c>
       <c r="E4" t="n">
-        <v>6001289</v>
+        <v>2877136</v>
       </c>
       <c r="F4" t="n">
-        <v>78251</v>
+        <v>62686</v>
       </c>
       <c r="G4" t="n">
-        <v>675</v>
+        <v>616</v>
       </c>
       <c r="H4" t="n">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="I4" t="n">
         <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>770</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>474262</v>
+        <v>346391</v>
       </c>
       <c r="L4" t="n">
-        <v>608824</v>
+        <v>400888</v>
       </c>
       <c r="M4" t="n">
-        <v>181765</v>
+        <v>139788</v>
       </c>
       <c r="N4" t="n">
-        <v>96866</v>
+        <v>51190</v>
       </c>
       <c r="O4" t="n">
-        <v>116678</v>
+        <v>78661</v>
       </c>
       <c r="P4" t="n">
-        <v>8374</v>
+        <v>7296</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9614642858505249</v>
+        <v>0.9438777565956116</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9144972562789917</v>
+        <v>0.8802111744880676</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8566983938217163</v>
+        <v>0.8061456680297852</v>
       </c>
       <c r="U4" t="n">
-        <v>0.352809727191925</v>
+        <v>0.2666073739528656</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8769211769104004</v>
+        <v>0.8326641321182251</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8680766224861145</v>
+        <v>0.828574001789093</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>26321</v>
+        <v>17742</v>
       </c>
       <c r="E5" t="n">
-        <v>261747</v>
+        <v>158466</v>
       </c>
       <c r="F5" t="n">
-        <v>1532307</v>
+        <v>723594</v>
       </c>
       <c r="G5" t="n">
-        <v>20913</v>
+        <v>10508</v>
       </c>
       <c r="H5" t="n">
-        <v>21503</v>
+        <v>21127</v>
       </c>
       <c r="I5" t="n">
         <v>375</v>
@@ -1080,131 +1080,131 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>308469</v>
+        <v>225451</v>
       </c>
       <c r="L5" t="n">
-        <v>513381</v>
+        <v>382217</v>
       </c>
       <c r="M5" t="n">
-        <v>330859</v>
+        <v>208218</v>
       </c>
       <c r="N5" t="n">
-        <v>119181</v>
+        <v>67492</v>
       </c>
       <c r="O5" t="n">
-        <v>131969</v>
+        <v>89812</v>
       </c>
       <c r="P5" t="n">
-        <v>83680</v>
+        <v>51409</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9760333895683289</v>
+        <v>0.9649812579154968</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9656389355659485</v>
+        <v>0.9520438313484192</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9843038320541382</v>
+        <v>0.978688657283783</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9933847784996033</v>
+        <v>0.9927321076393127</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9923866391181946</v>
+        <v>0.9896829724311829</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9971813559532166</v>
+        <v>0.9964050054550171</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>14063</v>
+        <v>10335</v>
       </c>
       <c r="E6" t="n">
-        <v>40707</v>
+        <v>17778</v>
       </c>
       <c r="F6" t="n">
-        <v>51448</v>
+        <v>32339</v>
       </c>
       <c r="G6" t="n">
-        <v>58888</v>
+        <v>21572</v>
       </c>
       <c r="H6" t="n">
-        <v>12796</v>
+        <v>6924</v>
       </c>
       <c r="I6" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="F7" t="n">
-        <v>49391</v>
+        <v>42988</v>
       </c>
       <c r="G7" t="n">
-        <v>73689</v>
+        <v>39014</v>
       </c>
       <c r="H7" t="n">
-        <v>885789</v>
+        <v>419161</v>
       </c>
       <c r="I7" t="n">
-        <v>7842</v>
+        <v>6799</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>555</v>
+        <v>481</v>
       </c>
       <c r="G8" t="n">
-        <v>1270</v>
+        <v>860</v>
       </c>
       <c r="H8" t="n">
-        <v>81675</v>
+        <v>49930</v>
       </c>
       <c r="I8" t="n">
-        <v>302865</v>
+        <v>141873</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
